--- a/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_single_phase_meter_7.xlsx
+++ b/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_single_phase_meter_7.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:00.731</t>
+          <t>2026/6/30 00:00:00.731</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -491,7 +491,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:05.387</t>
+          <t>2026/6/30 00:00:05.387</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -516,7 +516,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:10.041</t>
+          <t>2026/6/30 00:00:10.041</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -541,7 +541,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:14.689</t>
+          <t>2026/6/30 00:00:14.689</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:20.296</t>
+          <t>2026/6/30 00:00:20.296</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:24.974</t>
+          <t>2026/6/30 00:00:24.974</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -616,7 +616,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:29.610</t>
+          <t>2026/6/30 00:00:29.610</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:34.314</t>
+          <t>2026/6/30 00:00:34.314</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -666,7 +666,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:39.246</t>
+          <t>2026/6/30 00:00:39.246</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -691,7 +691,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:44.229</t>
+          <t>2026/6/30 00:00:44.229</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:48.884</t>
+          <t>2026/6/30 00:00:48.884</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:53.557</t>
+          <t>2026/6/30 00:00:53.557</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:59.470</t>
+          <t>2026/6/30 00:00:59.470</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:04.132</t>
+          <t>2026/6/30 00:01:04.132</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:08.797</t>
+          <t>2026/6/30 00:01:08.797</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:13.461</t>
+          <t>2026/6/30 00:01:13.461</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -866,7 +866,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:18.747</t>
+          <t>2026/6/30 00:01:18.747</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:23.699</t>
+          <t>2026/6/30 00:01:23.699</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:33.010</t>
+          <t>2026/6/30 00:01:33.010</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:38.000</t>
+          <t>2026/6/30 00:01:38.000</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:43.301</t>
+          <t>2026/6/30 00:01:43.301</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -991,7 +991,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:47.971</t>
+          <t>2026/6/30 00:01:47.971</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:52.606</t>
+          <t>2026/6/30 00:01:52.606</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:58.228</t>
+          <t>2026/6/30 00:01:58.228</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:03.170</t>
+          <t>2026/6/30 00:02:03.170</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:07.867</t>
+          <t>2026/6/30 00:02:07.867</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:12.505</t>
+          <t>2026/6/30 00:02:12.505</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:17.515</t>
+          <t>2026/6/30 00:02:17.515</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:22.777</t>
+          <t>2026/6/30 00:02:22.777</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:27.421</t>
+          <t>2026/6/30 00:02:27.421</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:32.118</t>
+          <t>2026/6/30 00:02:32.118</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:37.073</t>
+          <t>2026/6/30 00:02:37.073</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:42.373</t>
+          <t>2026/6/30 00:02:42.373</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:46.993</t>
+          <t>2026/6/30 00:02:46.993</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:51.694</t>
+          <t>2026/6/30 00:02:51.694</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:56.676</t>
+          <t>2026/6/30 00:02:56.676</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:02.263</t>
+          <t>2026/6/30 00:03:02.263</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:06.892</t>
+          <t>2026/6/30 00:03:06.892</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:11.565</t>
+          <t>2026/6/30 00:03:11.565</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:16.559</t>
+          <t>2026/6/30 00:03:16.559</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:21.524</t>
+          <t>2026/6/30 00:03:21.524</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:26.166</t>
+          <t>2026/6/30 00:03:26.166</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:30.880</t>
+          <t>2026/6/30 00:03:30.880</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:35.507</t>
+          <t>2026/6/30 00:03:35.507</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:41.131</t>
+          <t>2026/6/30 00:03:41.131</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:45.787</t>
+          <t>2026/6/30 00:03:45.787</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:50.415</t>
+          <t>2026/6/30 00:03:50.415</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:55.078</t>
+          <t>2026/6/30 00:03:55.078</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:01.028</t>
+          <t>2026/6/30 00:04:01.028</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:05.674</t>
+          <t>2026/6/30 00:04:05.674</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:10.334</t>
+          <t>2026/6/30 00:04:10.334</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:14.971</t>
+          <t>2026/6/30 00:04:14.971</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:19.646</t>
+          <t>2026/6/30 00:04:19.646</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:24.606</t>
+          <t>2026/6/30 00:04:24.606</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:29.299</t>
+          <t>2026/6/30 00:04:29.299</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:33.939</t>
+          <t>2026/6/30 00:04:33.939</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:39.229</t>
+          <t>2026/6/30 00:04:39.229</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:44.223</t>
+          <t>2026/6/30 00:04:44.223</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:48.887</t>
+          <t>2026/6/30 00:04:48.887</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:53.554</t>
+          <t>2026/6/30 00:04:53.554</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:59.462</t>
+          <t>2026/6/30 00:04:59.462</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:04.075</t>
+          <t>2026/6/30 00:05:04.075</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:09.395</t>
+          <t>2026/6/30 00:05:09.395</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:14.045</t>
+          <t>2026/6/30 00:05:14.045</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:19.326</t>
+          <t>2026/6/30 00:05:19.326</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:24.314</t>
+          <t>2026/6/30 00:05:24.314</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:28.972</t>
+          <t>2026/6/30 00:05:28.972</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:33.618</t>
+          <t>2026/6/30 00:05:33.618</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:38.933</t>
+          <t>2026/6/30 00:05:38.933</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:43.929</t>
+          <t>2026/6/30 00:05:43.929</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:48.593</t>
+          <t>2026/6/30 00:05:48.593</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:53.215</t>
+          <t>2026/6/30 00:05:53.215</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:58.818</t>
+          <t>2026/6/30 00:05:58.818</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:03.801</t>
+          <t>2026/6/30 00:06:03.801</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:13.125</t>
+          <t>2026/6/30 00:06:13.125</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:18.420</t>
+          <t>2026/6/30 00:06:18.420</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:18.420</t>
+          <t>2026/6/30 00:06:18.420</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:28.064</t>
+          <t>2026/6/30 00:06:28.064</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:32.739</t>
+          <t>2026/6/30 00:06:32.739</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:37.662</t>
+          <t>2026/6/30 00:06:37.662</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:42.984</t>
+          <t>2026/6/30 00:06:42.984</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:47.612</t>
+          <t>2026/6/30 00:06:47.612</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:52.288</t>
+          <t>2026/6/30 00:06:52.288</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:57.577</t>
+          <t>2026/6/30 00:06:57.577</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:02.862</t>
+          <t>2026/6/30 00:07:02.862</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:07.867</t>
+          <t>2026/6/30 00:07:07.867</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:12.506</t>
+          <t>2026/6/30 00:07:12.506</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:17.495</t>
+          <t>2026/6/30 00:07:17.495</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:22.763</t>
+          <t>2026/6/30 00:07:22.763</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:27.427</t>
+          <t>2026/6/30 00:07:27.427</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:32.107</t>
+          <t>2026/6/30 00:07:32.107</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:37.051</t>
+          <t>2026/6/30 00:07:37.051</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:42.338</t>
+          <t>2026/6/30 00:07:42.338</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:47.004</t>
+          <t>2026/6/30 00:07:47.004</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:51.692</t>
+          <t>2026/6/30 00:07:51.692</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:56.328</t>
+          <t>2026/6/30 00:07:56.328</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:00.962</t>
+          <t>2026/6/30 00:08:00.962</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:05.665</t>
+          <t>2026/6/30 00:08:05.665</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:10.349</t>
+          <t>2026/6/30 00:08:10.349</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:14.992</t>
+          <t>2026/6/30 00:08:14.992</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:20.578</t>
+          <t>2026/6/30 00:08:20.578</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:25.231</t>
+          <t>2026/6/30 00:08:25.231</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:29.882</t>
+          <t>2026/6/30 00:08:29.882</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:34.592</t>
+          <t>2026/6/30 00:08:34.592</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:39.873</t>
+          <t>2026/6/30 00:08:39.873</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:44.812</t>
+          <t>2026/6/30 00:08:44.812</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:49.486</t>
+          <t>2026/6/30 00:08:49.486</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:54.146</t>
+          <t>2026/6/30 00:08:54.146</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:00.078</t>
+          <t>2026/6/30 00:09:00.078</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:04.736</t>
+          <t>2026/6/30 00:09:04.736</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:09.405</t>
+          <t>2026/6/30 00:09:09.405</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:14.055</t>
+          <t>2026/6/30 00:09:14.055</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:19.351</t>
+          <t>2026/6/30 00:09:19.351</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:24.325</t>
+          <t>2026/6/30 00:09:24.325</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:28.996</t>
+          <t>2026/6/30 00:09:28.996</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:33.625</t>
+          <t>2026/6/30 00:09:33.625</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:38.910</t>
+          <t>2026/6/30 00:09:38.910</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:43.875</t>
+          <t>2026/6/30 00:09:43.875</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:48.548</t>
+          <t>2026/6/30 00:09:48.548</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:53.238</t>
+          <t>2026/6/30 00:09:53.238</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:58.786</t>
+          <t>2026/6/30 00:09:58.786</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:03.803</t>
+          <t>2026/6/30 00:10:03.803</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:13.105</t>
+          <t>2026/6/30 00:10:13.105</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:18.399</t>
+          <t>2026/6/30 00:10:18.399</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:18.399</t>
+          <t>2026/6/30 00:10:18.399</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:28.054</t>
+          <t>2026/6/30 00:10:28.054</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:32.728</t>
+          <t>2026/6/30 00:10:32.728</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:37.678</t>
+          <t>2026/6/30 00:10:37.678</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:42.977</t>
+          <t>2026/6/30 00:10:42.977</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:47.623</t>
+          <t>2026/6/30 00:10:47.623</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:52.302</t>
+          <t>2026/6/30 00:10:52.302</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:57.570</t>
+          <t>2026/6/30 00:10:57.570</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:02.833</t>
+          <t>2026/6/30 00:11:02.833</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:07.545</t>
+          <t>2026/6/30 00:11:07.545</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:12.170</t>
+          <t>2026/6/30 00:11:12.170</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:17.144</t>
+          <t>2026/6/30 00:11:17.144</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:22.440</t>
+          <t>2026/6/30 00:11:22.440</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:27.108</t>
+          <t>2026/6/30 00:11:27.108</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:31.757</t>
+          <t>2026/6/30 00:11:31.757</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:36.730</t>
+          <t>2026/6/30 00:11:36.730</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:41.422</t>
+          <t>2026/6/30 00:11:41.422</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:46.068</t>
+          <t>2026/6/30 00:11:46.068</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:50.719</t>
+          <t>2026/6/30 00:11:50.719</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:55.365</t>
+          <t>2026/6/30 00:11:55.365</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:01.279</t>
+          <t>2026/6/30 00:12:01.279</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:05.947</t>
+          <t>2026/6/30 00:12:05.947</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:10.620</t>
+          <t>2026/6/30 00:12:10.620</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:15.271</t>
+          <t>2026/6/30 00:12:15.271</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:20.869</t>
+          <t>2026/6/30 00:12:20.869</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:25.522</t>
+          <t>2026/6/30 00:12:25.522</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:30.221</t>
+          <t>2026/6/30 00:12:30.221</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:34.874</t>
+          <t>2026/6/30 00:12:34.874</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:40.122</t>
+          <t>2026/6/30 00:12:40.122</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:44.795</t>
+          <t>2026/6/30 00:12:44.795</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:49.501</t>
+          <t>2026/6/30 00:12:49.501</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:54.145</t>
+          <t>2026/6/30 00:12:54.145</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:00.076</t>
+          <t>2026/6/30 00:13:00.076</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:04.731</t>
+          <t>2026/6/30 00:13:04.731</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:09.391</t>
+          <t>2026/6/30 00:13:09.391</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:14.005</t>
+          <t>2026/6/30 00:13:14.005</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:19.319</t>
+          <t>2026/6/30 00:13:19.319</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:24.288</t>
+          <t>2026/6/30 00:13:24.288</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:28.971</t>
+          <t>2026/6/30 00:13:28.971</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:33.640</t>
+          <t>2026/6/30 00:13:33.640</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:38.929</t>
+          <t>2026/6/30 00:13:38.929</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:43.881</t>
+          <t>2026/6/30 00:13:43.881</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:53.185</t>
+          <t>2026/6/30 00:13:53.185</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:53.185</t>
+          <t>2026/6/30 00:13:53.185</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:58.805</t>
+          <t>2026/6/30 00:13:58.805</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:03.791</t>
+          <t>2026/6/30 00:14:03.791</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:13.122</t>
+          <t>2026/6/30 00:14:13.122</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:18.387</t>
+          <t>2026/6/30 00:14:18.387</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:23.356</t>
+          <t>2026/6/30 00:14:23.356</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:28.038</t>
+          <t>2026/6/30 00:14:28.038</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:32.688</t>
+          <t>2026/6/30 00:14:32.688</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:37.652</t>
+          <t>2026/6/30 00:14:37.652</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:42.927</t>
+          <t>2026/6/30 00:14:42.927</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:47.627</t>
+          <t>2026/6/30 00:14:47.627</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:52.310</t>
+          <t>2026/6/30 00:14:52.310</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:57.534</t>
+          <t>2026/6/30 00:14:57.534</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:02.851</t>
+          <t>2026/6/30 00:15:02.851</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:07.481</t>
+          <t>2026/6/30 00:15:07.481</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:12.198</t>
+          <t>2026/6/30 00:15:12.198</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:17.136</t>
+          <t>2026/6/30 00:15:17.136</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:22.086</t>
+          <t>2026/6/30 00:15:22.086</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:26.801</t>
+          <t>2026/6/30 00:15:26.801</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:31.453</t>
+          <t>2026/6/30 00:15:31.453</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:36.077</t>
+          <t>2026/6/30 00:15:36.077</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:41.711</t>
+          <t>2026/6/30 00:15:41.711</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:46.368</t>
+          <t>2026/6/30 00:15:46.368</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:51.030</t>
+          <t>2026/6/30 00:15:51.030</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:55.670</t>
+          <t>2026/6/30 00:15:55.670</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:01.593</t>
+          <t>2026/6/30 00:16:01.593</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:06.238</t>
+          <t>2026/6/30 00:16:06.238</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:10.888</t>
+          <t>2026/6/30 00:16:10.888</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:15.607</t>
+          <t>2026/6/30 00:16:15.607</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:20.532</t>
+          <t>2026/6/30 00:16:20.532</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:25.215</t>
+          <t>2026/6/30 00:16:25.215</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:29.895</t>
+          <t>2026/6/30 00:16:29.895</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:34.552</t>
+          <t>2026/6/30 00:16:34.552</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:39.821</t>
+          <t>2026/6/30 00:16:39.821</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:44.800</t>
+          <t>2026/6/30 00:16:44.800</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:49.467</t>
+          <t>2026/6/30 00:16:49.467</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:54.124</t>
+          <t>2026/6/30 00:16:54.124</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:00.051</t>
+          <t>2026/6/30 00:17:00.051</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:04.678</t>
+          <t>2026/6/30 00:17:04.678</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:09.364</t>
+          <t>2026/6/30 00:17:09.364</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:14.034</t>
+          <t>2026/6/30 00:17:14.034</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:19.298</t>
+          <t>2026/6/30 00:17:19.298</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:24.251</t>
+          <t>2026/6/30 00:17:24.251</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:28.930</t>
+          <t>2026/6/30 00:17:28.930</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:33.631</t>
+          <t>2026/6/30 00:17:33.631</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:38.881</t>
+          <t>2026/6/30 00:17:38.881</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:43.854</t>
+          <t>2026/6/30 00:17:43.854</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:53.151</t>
+          <t>2026/6/30 00:17:53.151</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:53.151</t>
+          <t>2026/6/30 00:17:53.151</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:58.793</t>
+          <t>2026/6/30 00:17:58.793</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:03.748</t>
+          <t>2026/6/30 00:18:03.748</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:13.081</t>
+          <t>2026/6/30 00:18:13.081</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:18.019</t>
+          <t>2026/6/30 00:18:18.019</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:23.354</t>
+          <t>2026/6/30 00:18:23.354</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:28.001</t>
+          <t>2026/6/30 00:18:28.001</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:32.643</t>
+          <t>2026/6/30 00:18:32.643</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:37.651</t>
+          <t>2026/6/30 00:18:37.651</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:42.890</t>
+          <t>2026/6/30 00:18:42.890</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:47.568</t>
+          <t>2026/6/30 00:18:47.568</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:52.220</t>
+          <t>2026/6/30 00:18:52.220</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:57.509</t>
+          <t>2026/6/30 00:18:57.509</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:02.824</t>
+          <t>2026/6/30 00:19:02.824</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:07.495</t>
+          <t>2026/6/30 00:19:07.495</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:12.153</t>
+          <t>2026/6/30 00:19:12.153</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:17.124</t>
+          <t>2026/6/30 00:19:17.124</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:22.365</t>
+          <t>2026/6/30 00:19:22.365</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:27.034</t>
+          <t>2026/6/30 00:19:27.034</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:31.700</t>
+          <t>2026/6/30 00:19:31.700</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:36.731</t>
+          <t>2026/6/30 00:19:36.731</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:41.981</t>
+          <t>2026/6/30 00:19:41.981</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:46.650</t>
+          <t>2026/6/30 00:19:46.650</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:51.320</t>
+          <t>2026/6/30 00:19:51.320</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:55.947</t>
+          <t>2026/6/30 00:19:55.947</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:00.928</t>
+          <t>2026/6/30 00:20:00.928</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:05.913</t>
+          <t>2026/6/30 00:20:05.913</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:10.562</t>
+          <t>2026/6/30 00:20:10.562</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:15.259</t>
+          <t>2026/6/30 00:20:15.259</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:20.824</t>
+          <t>2026/6/30 00:20:20.824</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:25.532</t>
+          <t>2026/6/30 00:20:25.532</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:30.159</t>
+          <t>2026/6/30 00:20:30.159</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:34.833</t>
+          <t>2026/6/30 00:20:34.833</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:40.132</t>
+          <t>2026/6/30 00:20:40.132</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:45.075</t>
+          <t>2026/6/30 00:20:45.075</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:49.723</t>
+          <t>2026/6/30 00:20:49.723</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:54.417</t>
+          <t>2026/6/30 00:20:54.417</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:59.986</t>
+          <t>2026/6/30 00:20:59.986</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:04.680</t>
+          <t>2026/6/30 00:21:04.680</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:09.330</t>
+          <t>2026/6/30 00:21:09.330</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:13.989</t>
+          <t>2026/6/30 00:21:13.989</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:19.275</t>
+          <t>2026/6/30 00:21:19.275</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:24.241</t>
+          <t>2026/6/30 00:21:24.241</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:28.900</t>
+          <t>2026/6/30 00:21:28.900</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:33.571</t>
+          <t>2026/6/30 00:21:33.571</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:38.856</t>
+          <t>2026/6/30 00:21:38.856</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:43.854</t>
+          <t>2026/6/30 00:21:43.854</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:53.159</t>
+          <t>2026/6/30 00:21:53.159</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:58.734</t>
+          <t>2026/6/30 00:21:58.734</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:58.734</t>
+          <t>2026/6/30 00:21:58.734</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:03.749</t>
+          <t>2026/6/30 00:22:03.749</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:13.087</t>
+          <t>2026/6/30 00:22:13.087</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:18.013</t>
+          <t>2026/6/30 00:22:18.013</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:23.312</t>
+          <t>2026/6/30 00:22:23.312</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:27.949</t>
+          <t>2026/6/30 00:22:27.949</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:32.626</t>
+          <t>2026/6/30 00:22:32.626</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:37.640</t>
+          <t>2026/6/30 00:22:37.640</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:42.921</t>
+          <t>2026/6/30 00:22:42.921</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:47.566</t>
+          <t>2026/6/30 00:22:47.566</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:52.202</t>
+          <t>2026/6/30 00:22:52.202</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:57.521</t>
+          <t>2026/6/30 00:22:57.521</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:02.782</t>
+          <t>2026/6/30 00:23:02.782</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:07.470</t>
+          <t>2026/6/30 00:23:07.470</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:12.120</t>
+          <t>2026/6/30 00:23:12.120</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:17.108</t>
+          <t>2026/6/30 00:23:17.108</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:22.386</t>
+          <t>2026/6/30 00:23:22.386</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:27.031</t>
+          <t>2026/6/30 00:23:27.031</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:31.699</t>
+          <t>2026/6/30 00:23:31.699</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:36.683</t>
+          <t>2026/6/30 00:23:36.683</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:41.638</t>
+          <t>2026/6/30 00:23:41.638</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:46.622</t>
+          <t>2026/6/30 00:23:46.622</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:51.271</t>
+          <t>2026/6/30 00:23:51.271</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:56.266</t>
+          <t>2026/6/30 00:23:56.266</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:01.869</t>
+          <t>2026/6/30 00:24:01.869</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:06.530</t>
+          <t>2026/6/30 00:24:06.530</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:11.177</t>
+          <t>2026/6/30 00:24:11.177</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:15.855</t>
+          <t>2026/6/30 00:24:15.855</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:21.452</t>
+          <t>2026/6/30 00:24:21.452</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:26.120</t>
+          <t>2026/6/30 00:24:26.120</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:30.786</t>
+          <t>2026/6/30 00:24:30.786</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:35.438</t>
+          <t>2026/6/30 00:24:35.438</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:40.432</t>
+          <t>2026/6/30 00:24:40.432</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:45.099</t>
+          <t>2026/6/30 00:24:45.099</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:49.747</t>
+          <t>2026/6/30 00:24:49.747</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:54.415</t>
+          <t>2026/6/30 00:24:54.415</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:00.326</t>
+          <t>2026/6/30 00:25:00.326</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:04.985</t>
+          <t>2026/6/30 00:25:04.985</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:09.638</t>
+          <t>2026/6/30 00:25:09.638</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:14.300</t>
+          <t>2026/6/30 00:25:14.300</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:19.597</t>
+          <t>2026/6/30 00:25:19.597</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:24.585</t>
+          <t>2026/6/30 00:25:24.585</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:29.218</t>
+          <t>2026/6/30 00:25:29.218</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:33.895</t>
+          <t>2026/6/30 00:25:33.895</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:39.179</t>
+          <t>2026/6/30 00:25:39.179</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:44.150</t>
+          <t>2026/6/30 00:25:44.150</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:48.826</t>
+          <t>2026/6/30 00:25:48.826</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:53.472</t>
+          <t>2026/6/30 00:25:53.472</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:59.387</t>
+          <t>2026/6/30 00:25:59.387</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:04.048</t>
+          <t>2026/6/30 00:26:04.048</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:13.333</t>
+          <t>2026/6/30 00:26:13.333</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:18.669</t>
+          <t>2026/6/30 00:26:18.669</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:18.669</t>
+          <t>2026/6/30 00:26:18.669</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:28.254</t>
+          <t>2026/6/30 00:26:28.254</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:32.920</t>
+          <t>2026/6/30 00:26:32.920</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:38.242</t>
+          <t>2026/6/30 00:26:38.242</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:43.207</t>
+          <t>2026/6/30 00:26:43.207</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:47.890</t>
+          <t>2026/6/30 00:26:47.890</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:52.514</t>
+          <t>2026/6/30 00:26:52.514</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:57.820</t>
+          <t>2026/6/30 00:26:57.820</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:03.115</t>
+          <t>2026/6/30 00:27:03.115</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:07.752</t>
+          <t>2026/6/30 00:27:07.752</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:12.407</t>
+          <t>2026/6/30 00:27:12.407</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:17.403</t>
+          <t>2026/6/30 00:27:17.403</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:22.714</t>
+          <t>2026/6/30 00:27:22.714</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:27.636</t>
+          <t>2026/6/30 00:27:27.636</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:32.332</t>
+          <t>2026/6/30 00:27:32.332</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:37.280</t>
+          <t>2026/6/30 00:27:37.280</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:42.569</t>
+          <t>2026/6/30 00:27:42.569</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:47.238</t>
+          <t>2026/6/30 00:27:47.238</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:51.935</t>
+          <t>2026/6/30 00:27:51.935</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:57.211</t>
+          <t>2026/6/30 00:27:57.211</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:02.474</t>
+          <t>2026/6/30 00:28:02.474</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:07.140</t>
+          <t>2026/6/30 00:28:07.140</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:11.799</t>
+          <t>2026/6/30 00:28:11.799</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:16.456</t>
+          <t>2026/6/30 00:28:16.456</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:21.130</t>
+          <t>2026/6/30 00:28:21.130</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:25.810</t>
+          <t>2026/6/30 00:28:25.810</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:30.453</t>
+          <t>2026/6/30 00:28:30.453</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:35.096</t>
+          <t>2026/6/30 00:28:35.096</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:40.730</t>
+          <t>2026/6/30 00:28:40.730</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:45.358</t>
+          <t>2026/6/30 00:28:45.358</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:50.022</t>
+          <t>2026/6/30 00:28:50.022</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:54.702</t>
+          <t>2026/6/30 00:28:54.702</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:00.599</t>
+          <t>2026/6/30 00:29:00.599</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:05.263</t>
+          <t>2026/6/30 00:29:05.263</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:09.918</t>
+          <t>2026/6/30 00:29:09.918</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:14.597</t>
+          <t>2026/6/30 00:29:14.597</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:19.892</t>
+          <t>2026/6/30 00:29:19.892</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:24.870</t>
+          <t>2026/6/30 00:29:24.870</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:29.529</t>
+          <t>2026/6/30 00:29:29.529</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:34.180</t>
+          <t>2026/6/30 00:29:34.180</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:39.454</t>
+          <t>2026/6/30 00:29:39.454</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:44.461</t>
+          <t>2026/6/30 00:29:44.461</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:49.102</t>
+          <t>2026/6/30 00:29:49.102</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:53.777</t>
+          <t>2026/6/30 00:29:53.777</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:59.649</t>
+          <t>2026/6/30 00:29:59.649</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:04.340</t>
+          <t>2026/6/30 00:30:04.340</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:08.992</t>
+          <t>2026/6/30 00:30:08.992</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:13.663</t>
+          <t>2026/6/30 00:30:13.663</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:18.951</t>
+          <t>2026/6/30 00:30:18.951</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:23.920</t>
+          <t>2026/6/30 00:30:23.920</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:33.275</t>
+          <t>2026/6/30 00:30:33.275</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:38.529</t>
+          <t>2026/6/30 00:30:38.529</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:43.504</t>
+          <t>2026/6/30 00:30:43.504</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:48.183</t>
+          <t>2026/6/30 00:30:48.183</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:52.846</t>
+          <t>2026/6/30 00:30:52.846</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:58.442</t>
+          <t>2026/6/30 00:30:58.442</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:03.410</t>
+          <t>2026/6/30 00:31:03.410</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:08.042</t>
+          <t>2026/6/30 00:31:08.042</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:12.703</t>
+          <t>2026/6/30 00:31:12.703</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:17.693</t>
+          <t>2026/6/30 00:31:17.693</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:22.945</t>
+          <t>2026/6/30 00:31:22.945</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:27.653</t>
+          <t>2026/6/30 00:31:27.653</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:32.281</t>
+          <t>2026/6/30 00:31:32.281</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:37.272</t>
+          <t>2026/6/30 00:31:37.272</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:42.552</t>
+          <t>2026/6/30 00:31:42.552</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:47.233</t>
+          <t>2026/6/30 00:31:47.233</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:51.871</t>
+          <t>2026/6/30 00:31:51.871</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:57.153</t>
+          <t>2026/6/30 00:31:57.153</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:02.153</t>
+          <t>2026/6/30 00:32:02.153</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:07.137</t>
+          <t>2026/6/30 00:32:07.137</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:11.758</t>
+          <t>2026/6/30 00:32:11.758</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:16.771</t>
+          <t>2026/6/30 00:32:16.771</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:22.032</t>
+          <t>2026/6/30 00:32:22.032</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:26.716</t>
+          <t>2026/6/30 00:32:26.716</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:31.371</t>
+          <t>2026/6/30 00:32:31.371</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:36.043</t>
+          <t>2026/6/30 00:32:36.043</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:41.645</t>
+          <t>2026/6/30 00:32:41.645</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:46.277</t>
+          <t>2026/6/30 00:32:46.277</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:50.949</t>
+          <t>2026/6/30 00:32:50.949</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:55.610</t>
+          <t>2026/6/30 00:32:55.610</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:00.897</t>
+          <t>2026/6/30 00:33:00.897</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:05.534</t>
+          <t>2026/6/30 00:33:05.534</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:10.238</t>
+          <t>2026/6/30 00:33:10.238</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:14.860</t>
+          <t>2026/6/30 00:33:14.860</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:20.493</t>
+          <t>2026/6/30 00:33:20.493</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:25.136</t>
+          <t>2026/6/30 00:33:25.136</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:29.797</t>
+          <t>2026/6/30 00:33:29.797</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:34.494</t>
+          <t>2026/6/30 00:33:34.494</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:39.734</t>
+          <t>2026/6/30 00:33:39.734</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:44.718</t>
+          <t>2026/6/30 00:33:44.718</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:49.410</t>
+          <t>2026/6/30 00:33:49.410</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:54.058</t>
+          <t>2026/6/30 00:33:54.058</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:59.944</t>
+          <t>2026/6/30 00:33:59.944</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:04.605</t>
+          <t>2026/6/30 00:34:04.605</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:09.267</t>
+          <t>2026/6/30 00:34:09.267</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:13.945</t>
+          <t>2026/6/30 00:34:13.945</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:19.227</t>
+          <t>2026/6/30 00:34:19.227</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:24.181</t>
+          <t>2026/6/30 00:34:24.181</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:28.866</t>
+          <t>2026/6/30 00:34:28.866</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:33.527</t>
+          <t>2026/6/30 00:34:33.527</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:38.803</t>
+          <t>2026/6/30 00:34:38.803</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:43.787</t>
+          <t>2026/6/30 00:34:43.787</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:53.114</t>
+          <t>2026/6/30 00:34:53.114</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:58.712</t>
+          <t>2026/6/30 00:34:58.712</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:58.712</t>
+          <t>2026/6/30 00:34:58.712</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:08.329</t>
+          <t>2026/6/30 00:35:08.329</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:13.019</t>
+          <t>2026/6/30 00:35:13.019</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:17.959</t>
+          <t>2026/6/30 00:35:17.959</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:23.288</t>
+          <t>2026/6/30 00:35:23.288</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:27.934</t>
+          <t>2026/6/30 00:35:27.934</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:32.562</t>
+          <t>2026/6/30 00:35:32.562</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:37.547</t>
+          <t>2026/6/30 00:35:37.547</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:42.521</t>
+          <t>2026/6/30 00:35:42.521</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:47.202</t>
+          <t>2026/6/30 00:35:47.202</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:51.837</t>
+          <t>2026/6/30 00:35:51.837</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:56.806</t>
+          <t>2026/6/30 00:35:56.806</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:02.427</t>
+          <t>2026/6/30 00:36:02.427</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:07.084</t>
+          <t>2026/6/30 00:36:07.084</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:11.760</t>
+          <t>2026/6/30 00:36:11.760</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:16.700</t>
+          <t>2026/6/30 00:36:16.700</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:22.024</t>
+          <t>2026/6/30 00:36:22.024</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:26.653</t>
+          <t>2026/6/30 00:36:26.653</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:31.361</t>
+          <t>2026/6/30 00:36:31.361</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:36.020</t>
+          <t>2026/6/30 00:36:36.020</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:40.965</t>
+          <t>2026/6/30 00:36:40.965</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:45.645</t>
+          <t>2026/6/30 00:36:45.645</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:50.308</t>
+          <t>2026/6/30 00:36:50.308</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:54.971</t>
+          <t>2026/6/30 00:36:54.971</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:00.855</t>
+          <t>2026/6/30 00:37:00.855</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:05.549</t>
+          <t>2026/6/30 00:37:05.549</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:10.184</t>
+          <t>2026/6/30 00:37:10.184</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:14.879</t>
+          <t>2026/6/30 00:37:14.879</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:20.443</t>
+          <t>2026/6/30 00:37:20.443</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:25.112</t>
+          <t>2026/6/30 00:37:25.112</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:29.758</t>
+          <t>2026/6/30 00:37:29.758</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:34.428</t>
+          <t>2026/6/30 00:37:34.428</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:39.744</t>
+          <t>2026/6/30 00:37:39.744</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:44.704</t>
+          <t>2026/6/30 00:37:44.704</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:49.353</t>
+          <t>2026/6/30 00:37:49.353</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:54.030</t>
+          <t>2026/6/30 00:37:54.030</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:59.947</t>
+          <t>2026/6/30 00:37:59.947</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:05.212</t>
+          <t>2026/6/30 00:38:05.212</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:09.905</t>
+          <t>2026/6/30 00:38:09.905</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:14.572</t>
+          <t>2026/6/30 00:38:14.572</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:19.841</t>
+          <t>2026/6/30 00:38:19.841</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:24.808</t>
+          <t>2026/6/30 00:38:24.808</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:29.468</t>
+          <t>2026/6/30 00:38:29.468</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:34.153</t>
+          <t>2026/6/30 00:38:34.153</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:39.419</t>
+          <t>2026/6/30 00:38:39.419</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:44.390</t>
+          <t>2026/6/30 00:38:44.390</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:49.035</t>
+          <t>2026/6/30 00:38:49.035</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:53.690</t>
+          <t>2026/6/30 00:38:53.690</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:59.608</t>
+          <t>2026/6/30 00:38:59.608</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:04.280</t>
+          <t>2026/6/30 00:39:04.280</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:08.933</t>
+          <t>2026/6/30 00:39:08.933</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:13.628</t>
+          <t>2026/6/30 00:39:13.628</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:18.886</t>
+          <t>2026/6/30 00:39:18.886</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:23.855</t>
+          <t>2026/6/30 00:39:23.855</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:33.214</t>
+          <t>2026/6/30 00:39:33.214</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:38.454</t>
+          <t>2026/6/30 00:39:38.454</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:43.449</t>
+          <t>2026/6/30 00:39:43.449</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:48.087</t>
+          <t>2026/6/30 00:39:48.087</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:52.791</t>
+          <t>2026/6/30 00:39:52.791</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:58.375</t>
+          <t>2026/6/30 00:39:58.375</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:03.353</t>
+          <t>2026/6/30 00:40:03.353</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:08.014</t>
+          <t>2026/6/30 00:40:08.014</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:12.680</t>
+          <t>2026/6/30 00:40:12.680</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:17.634</t>
+          <t>2026/6/30 00:40:17.634</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:22.629</t>
+          <t>2026/6/30 00:40:22.629</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:27.277</t>
+          <t>2026/6/30 00:40:27.277</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:31.950</t>
+          <t>2026/6/30 00:40:31.950</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:36.938</t>
+          <t>2026/6/30 00:40:36.938</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:42.191</t>
+          <t>2026/6/30 00:40:42.191</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:46.874</t>
+          <t>2026/6/30 00:40:46.874</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:51.518</t>
+          <t>2026/6/30 00:40:51.518</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:56.523</t>
+          <t>2026/6/30 00:40:56.523</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:02.099</t>
+          <t>2026/6/30 00:41:02.099</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:06.732</t>
+          <t>2026/6/30 00:41:06.732</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:11.426</t>
+          <t>2026/6/30 00:41:11.426</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:16.090</t>
+          <t>2026/6/30 00:41:16.090</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:20.745</t>
+          <t>2026/6/30 00:41:20.745</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:25.388</t>
+          <t>2026/6/30 00:41:25.388</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:30.059</t>
+          <t>2026/6/30 00:41:30.059</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:34.724</t>
+          <t>2026/6/30 00:41:34.724</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:39.403</t>
+          <t>2026/6/30 00:41:39.403</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:44.047</t>
+          <t>2026/6/30 00:41:44.047</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:53.388</t>
+          <t>2026/6/30 00:41:53.388</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:58.048</t>
+          <t>2026/6/30 00:41:58.048</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:02.708</t>
+          <t>2026/6/30 00:42:02.708</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:07.370</t>
+          <t>2026/6/30 00:42:07.370</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:12.049</t>
+          <t>2026/6/30 00:42:12.049</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:16.711</t>
+          <t>2026/6/30 00:42:16.711</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:21.341</t>
+          <t>2026/6/30 00:42:21.341</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:26.016</t>
+          <t>2026/6/30 00:42:26.016</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:30.668</t>
+          <t>2026/6/30 00:42:30.668</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:35.372</t>
+          <t>2026/6/30 00:42:35.372</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:40.005</t>
+          <t>2026/6/30 00:42:40.005</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:44.646</t>
+          <t>2026/6/30 00:42:44.646</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:49.336</t>
+          <t>2026/6/30 00:42:49.336</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:54.016</t>
+          <t>2026/6/30 00:42:54.016</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:03.324</t>
+          <t>2026/6/30 00:43:03.324</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:08.006</t>
+          <t>2026/6/30 00:43:08.006</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:12.623</t>
+          <t>2026/6/30 00:43:12.623</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:17.301</t>
+          <t>2026/6/30 00:43:17.301</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:21.977</t>
+          <t>2026/6/30 00:43:21.977</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:26.624</t>
+          <t>2026/6/30 00:43:26.624</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:31.295</t>
+          <t>2026/6/30 00:43:31.295</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:35.945</t>
+          <t>2026/6/30 00:43:35.945</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:40.608</t>
+          <t>2026/6/30 00:43:40.608</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:45.291</t>
+          <t>2026/6/30 00:43:45.291</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:49.969</t>
+          <t>2026/6/30 00:43:49.969</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:54.588</t>
+          <t>2026/6/30 00:43:54.588</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:59.301</t>
+          <t>2026/6/30 00:43:59.301</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:03.932</t>
+          <t>2026/6/30 00:44:03.932</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:13.294</t>
+          <t>2026/6/30 00:44:13.294</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:17.913</t>
+          <t>2026/6/30 00:44:17.913</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:22.592</t>
+          <t>2026/6/30 00:44:22.592</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:27.255</t>
+          <t>2026/6/30 00:44:27.255</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:31.929</t>
+          <t>2026/6/30 00:44:31.929</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:36.591</t>
+          <t>2026/6/30 00:44:36.591</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:41.243</t>
+          <t>2026/6/30 00:44:41.243</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:45.891</t>
+          <t>2026/6/30 00:44:45.891</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:50.552</t>
+          <t>2026/6/30 00:44:50.552</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:55.224</t>
+          <t>2026/6/30 00:44:55.224</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:59.881</t>
+          <t>2026/6/30 00:44:59.881</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:04.544</t>
+          <t>2026/6/30 00:45:04.544</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:09.207</t>
+          <t>2026/6/30 00:45:09.207</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:18.518</t>
+          <t>2026/6/30 00:45:18.518</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:23.224</t>
+          <t>2026/6/30 00:45:23.224</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:27.855</t>
+          <t>2026/6/30 00:45:27.855</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:32.510</t>
+          <t>2026/6/30 00:45:32.510</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:37.177</t>
+          <t>2026/6/30 00:45:37.177</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:41.831</t>
+          <t>2026/6/30 00:45:41.831</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:46.534</t>
+          <t>2026/6/30 00:45:46.534</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:51.156</t>
+          <t>2026/6/30 00:45:51.156</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:55.846</t>
+          <t>2026/6/30 00:45:55.846</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:00.485</t>
+          <t>2026/6/30 00:46:00.485</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:05.179</t>
+          <t>2026/6/30 00:46:05.179</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:09.850</t>
+          <t>2026/6/30 00:46:09.850</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:14.522</t>
+          <t>2026/6/30 00:46:14.522</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:19.149</t>
+          <t>2026/6/30 00:46:19.149</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:28.469</t>
+          <t>2026/6/30 00:46:28.469</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:33.140</t>
+          <t>2026/6/30 00:46:33.140</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:37.804</t>
+          <t>2026/6/30 00:46:37.804</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:42.464</t>
+          <t>2026/6/30 00:46:42.464</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:47.119</t>
+          <t>2026/6/30 00:46:47.119</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:51.823</t>
+          <t>2026/6/30 00:46:51.823</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:56.443</t>
+          <t>2026/6/30 00:46:56.443</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:01.121</t>
+          <t>2026/6/30 00:47:01.121</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:05.790</t>
+          <t>2026/6/30 00:47:05.790</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:10.434</t>
+          <t>2026/6/30 00:47:10.434</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:15.115</t>
+          <t>2026/6/30 00:47:15.115</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:19.788</t>
+          <t>2026/6/30 00:47:19.788</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:24.450</t>
+          <t>2026/6/30 00:47:24.450</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:29.091</t>
+          <t>2026/6/30 00:47:29.091</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:38.434</t>
+          <t>2026/6/30 00:47:38.434</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:43.079</t>
+          <t>2026/6/30 00:47:43.079</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:47.724</t>
+          <t>2026/6/30 00:47:47.724</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:52.376</t>
+          <t>2026/6/30 00:47:52.376</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:57.086</t>
+          <t>2026/6/30 00:47:57.086</t>
         </is>
       </c>
       <c r="C577" t="n">
